--- a/data/trans_camb/P16A03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A03-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,18</t>
+          <t>-2,62; 2,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 0,66</t>
+          <t>-3,76; 0,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,31</t>
+          <t>-3,21; 1,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 3,65</t>
+          <t>-5,57; 3,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 4,64</t>
+          <t>-3,75; 5,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 4,57</t>
+          <t>-3,02; 5,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,0</t>
+          <t>-2,98; 2,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,24</t>
+          <t>-3,12; 1,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,17</t>
+          <t>-2,25; 2,32</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-83,48; 233,99</t>
+          <t>-77,82; 274,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 150,58</t>
+          <t>-100,0; 149,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-80,62; 180,44</t>
+          <t>-81,74; 139,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,47; 83,08</t>
+          <t>-59,22; 71,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,85; 96,17</t>
+          <t>-45,08; 106,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,35; 98,32</t>
+          <t>-33,26; 116,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,68; 61,63</t>
+          <t>-51,06; 67,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,97; 71,31</t>
+          <t>-51,24; 58,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,77; 67,79</t>
+          <t>-37,54; 72,86</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,15</t>
+          <t>-2,08; 2,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,85</t>
+          <t>-2,64; 1,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,83</t>
+          <t>-2,96; 0,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,48</t>
+          <t>-1,43; 4,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,04</t>
+          <t>-4,36; 0,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,2</t>
+          <t>-3,86; 0,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,22</t>
+          <t>-1,11; 2,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,0</t>
+          <t>-2,86; 0,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,12</t>
+          <t>-2,69; 0,1</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,04; 299,36</t>
+          <t>-82,25; 283,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-83,67; 124,74</t>
+          <t>-84,33; 147,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,15; 134,41</t>
+          <t>-86,99; 185,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 139,06</t>
+          <t>-26,85; 140,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,83; 7,52</t>
+          <t>-75,86; 8,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,49; 10,59</t>
+          <t>-68,9; 16,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 91,57</t>
+          <t>-31,14; 104,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,36; 2,46</t>
+          <t>-72,97; 3,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-70,09; 5,88</t>
+          <t>-65,88; 7,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,07</t>
+          <t>-1,9; 1,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 0,45</t>
+          <t>-3,07; 0,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,89</t>
+          <t>0,73; 5,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 4,07</t>
+          <t>-3,19; 3,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 1,35</t>
+          <t>-5,29; 1,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,56</t>
+          <t>-0,62; 5,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,34</t>
+          <t>-1,67; 2,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,53</t>
+          <t>-3,3; 0,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,77</t>
+          <t>0,71; 4,98</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 622,62</t>
+          <t>-92,23; 622,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 1362,77</t>
+          <t>-7,06; 1471,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 116,4</t>
+          <t>-46,42; 109,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,47; 42,62</t>
+          <t>-74,71; 31,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 150,86</t>
+          <t>-7,97; 169,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,37; 96,26</t>
+          <t>-40,25; 99,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,33; 23,57</t>
+          <t>-74,35; 19,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,34; 201,43</t>
+          <t>15,32; 219,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,22</t>
+          <t>-3,9; 0,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,39</t>
+          <t>-3,75; 0,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 0,36</t>
+          <t>-4,14; 0,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 5,64</t>
+          <t>-2,26; 5,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,42</t>
+          <t>-2,91; 4,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -2,17</t>
+          <t>-7,97; -2,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 2,2</t>
+          <t>-2,25; 2,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,79</t>
+          <t>-2,53; 1,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,19; -1,63</t>
+          <t>-5,35; -1,51</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-88,87; 29,08</t>
+          <t>-85,88; 35,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-84,88; 33,58</t>
+          <t>-84,84; 24,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-91,68; 43,83</t>
+          <t>-91,9; 55,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 124,64</t>
+          <t>-29,06; 108,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 84,38</t>
+          <t>-35,1; 91,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,2; -37,87</t>
+          <t>-86,44; -36,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,44; 54,95</t>
+          <t>-37,21; 54,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,55; 46,2</t>
+          <t>-42,94; 47,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-81,21; -35,04</t>
+          <t>-82,14; -32,93</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 4,4</t>
+          <t>-0,31; 4,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,86</t>
+          <t>-1,37; 0,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,83</t>
+          <t>0,8; 4,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 9,94</t>
+          <t>-0,7; 10,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 1,75</t>
+          <t>-6,6; 1,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 7,56</t>
+          <t>-1,11; 7,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,79</t>
+          <t>0,24; 6,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,08</t>
+          <t>-3,25; 1,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,77</t>
+          <t>0,92; 5,57</t>
         </is>
       </c>
     </row>
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 332,6</t>
+          <t>-14,29; 370,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-80,66; 75,89</t>
+          <t>-81,82; 69,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 274,17</t>
+          <t>-17,81; 252,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 322,25</t>
+          <t>2,42; 350,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-77,6; 67,73</t>
+          <t>-77,0; 79,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16,45; 346,01</t>
+          <t>15,16; 355,56</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,47</t>
+          <t>-3,13; 0,5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,06</t>
+          <t>-2,78; 1,19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,09</t>
+          <t>-1,33; 2,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 2,38</t>
+          <t>-5,26; 2,24</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 0,66</t>
+          <t>-6,55; 0,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 4,0</t>
+          <t>-3,36; 3,79</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,86</t>
+          <t>-3,69; 0,69</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,37</t>
+          <t>-4,04; 0,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,74</t>
+          <t>-1,75; 2,73</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 226,53</t>
+          <t>-100,0; 224,06</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 184,1</t>
+          <t>-100,0; 299,0</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,97; 405,99</t>
+          <t>-46,78; 398,19</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-60,67; 52,6</t>
+          <t>-63,9; 56,38</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-76,42; 18,51</t>
+          <t>-72,76; 31,9</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-36,06; 96,32</t>
+          <t>-37,62; 95,06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-63,52; 31,5</t>
+          <t>-64,64; 26,19</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-69,97; 18,61</t>
+          <t>-73,48; 11,91</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-27,99; 94,74</t>
+          <t>-31,77; 89,13</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,53; -0,17</t>
+          <t>-3,48; -0,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,23</t>
+          <t>-2,38; 1,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,4</t>
+          <t>-1,04; 3,32</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,61</t>
+          <t>-2,59; 2,81</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,4</t>
+          <t>-5,3; -0,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 3,5</t>
+          <t>-4,41; 3,58</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,68</t>
+          <t>-2,67; 0,73</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,15</t>
+          <t>-3,32; -0,07</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,86</t>
+          <t>-1,55; 2,93</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-85,65; -0,31</t>
+          <t>-83,1; 13,62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-61,11; 58,43</t>
+          <t>-59,26; 63,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 159,46</t>
+          <t>-27,43; 161,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 50,61</t>
+          <t>-33,57; 54,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-64,98; -5,32</t>
+          <t>-66,24; -8,64</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-50,3; 58,37</t>
+          <t>-55,48; 61,0</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-45,16; 18,15</t>
+          <t>-45,31; 19,35</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-57,23; -3,77</t>
+          <t>-56,99; -0,51</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 70,8</t>
+          <t>-26,83; 71,64</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,12; -0,49</t>
+          <t>-3,26; -0,54</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,08; -0,34</t>
+          <t>-3,06; -0,35</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,61; -1,18</t>
+          <t>-3,84; -1,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,88</t>
+          <t>-0,86; 3,06</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,1</t>
+          <t>-1,52; 2,04</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,09; -0,16</t>
+          <t>-2,88; -0,04</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,81</t>
+          <t>-1,69; 0,84</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,45</t>
+          <t>-1,74; 0,54</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,94; -1,03</t>
+          <t>-3,11; -1,07</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-91,05; -20,12</t>
+          <t>-91,35; -19,75</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-88,61; -6,51</t>
+          <t>-85,74; -3,09</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -66,53</t>
+          <t>-100,0; -67,42</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 121,18</t>
+          <t>-22,41; 123,17</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 92,01</t>
+          <t>-38,23; 81,25</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-68,62; -1,82</t>
+          <t>-68,06; 2,17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 35,71</t>
+          <t>-45,73; 38,94</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-50,92; 20,39</t>
+          <t>-49,42; 26,83</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-82,96; -45,39</t>
+          <t>-83,03; -45,79</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,57; -0,23</t>
+          <t>-1,58; -0,25</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,64; -0,32</t>
+          <t>-1,61; -0,3</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,5</t>
+          <t>-1,1; 0,41</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,81</t>
+          <t>-0,47; 1,74</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,23; -0,04</t>
+          <t>-2,36; -0,14</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,65</t>
+          <t>-1,54; 0,61</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,58</t>
+          <t>-0,72; 0,67</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,65; -0,46</t>
+          <t>-1,65; -0,43</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,37</t>
+          <t>-0,96; 0,38</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-59,11; -11,67</t>
+          <t>-61,17; -12,84</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-61,24; -16,92</t>
+          <t>-60,5; -15,87</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-36,26; 27,09</t>
+          <t>-40,54; 22,73</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 37,79</t>
+          <t>-8,14; 37,26</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 0,45</t>
+          <t>-40,08; -3,02</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 13,09</t>
+          <t>-26,33; 13,14</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 17,27</t>
+          <t>-17,38; 19,7</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-40,7; -12,68</t>
+          <t>-39,86; -12,22</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 10,85</t>
+          <t>-23,47; 11,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A03-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>-0,26</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,54</t>
+          <t>-2,91; 2,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,78</t>
+          <t>-3,69; 0,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,2</t>
+          <t>-3,41; 0,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 3,15</t>
+          <t>-5,13; 3,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,16</t>
+          <t>-4,34; 4,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 5,02</t>
+          <t>-4,1; 3,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 2,0</t>
+          <t>-3,0; 2,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,86</t>
+          <t>-3,53; 1,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,32</t>
+          <t>-2,88; 1,69</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-34,26%</t>
+          <t>-37,42%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>-5,77%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-77,82; 274,45</t>
+          <t>-78,47; 281,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 149,18</t>
+          <t>-100,0; 117,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,74; 139,8</t>
+          <t>-85,26; 114,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 71,9</t>
+          <t>-57,56; 98,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,08; 106,16</t>
+          <t>-45,9; 88,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 116,54</t>
+          <t>-40,36; 88,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 67,62</t>
+          <t>-51,78; 71,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,24; 58,98</t>
+          <t>-54,86; 61,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,54; 72,86</t>
+          <t>-46,17; 51,82</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>-0,78</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,76</t>
+          <t>-1,73</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,29</t>
+          <t>-1,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,12</t>
+          <t>-2,26; 2,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,03</t>
+          <t>-2,8; 0,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,69</t>
+          <t>-2,71; 0,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,33</t>
+          <t>-1,37; 4,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,18</t>
+          <t>-4,21; 0,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,38</t>
+          <t>-4,02; 0,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,53</t>
+          <t>-1,1; 2,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,05</t>
+          <t>-2,77; 0,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,1</t>
+          <t>-2,78; 0,07</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-42,85%</t>
+          <t>-42,54%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-40,96%</t>
+          <t>-40,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-41,87%</t>
+          <t>-40,89%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,25; 283,6</t>
+          <t>-84,57; 268,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-84,33; 147,95</t>
+          <t>-84,23; 134,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-86,99; 185,24</t>
+          <t>-89,66; 148,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 140,47</t>
+          <t>-28,23; 138,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,86; 8,66</t>
+          <t>-77,88; 9,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,9; 16,81</t>
+          <t>-69,4; 12,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,14; 104,6</t>
+          <t>-27,71; 116,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,97; 3,95</t>
+          <t>-70,5; 1,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,88; 7,41</t>
+          <t>-67,22; 4,4</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,06</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,83</t>
+          <t>-1,98; 2,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,43</t>
+          <t>-2,92; 0,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,66</t>
+          <t>0,51; 5,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,91</t>
+          <t>-3,58; 3,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 1,15</t>
+          <t>-4,83; 1,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,54</t>
+          <t>-1,19; 5,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,34</t>
+          <t>-1,97; 2,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,4</t>
+          <t>-3,1; 0,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,98</t>
+          <t>0,52; 4,81</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>254,12%</t>
+          <t>240,56%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>81,34%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-92,23; 622,08</t>
+          <t>-100,0; 684,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 1471,96</t>
+          <t>-3,23; 1280,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,42; 109,32</t>
+          <t>-49,67; 102,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,71; 31,96</t>
+          <t>-69,16; 60,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 169,38</t>
+          <t>-17,77; 140,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,25; 99,0</t>
+          <t>-45,71; 89,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,35; 19,29</t>
+          <t>-74,8; 19,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,32; 219,13</t>
+          <t>9,91; 196,57</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,95</t>
+          <t>-2,11</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>-4,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,29</t>
+          <t>-3,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,36</t>
+          <t>-3,87; 0,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,41</t>
+          <t>-3,87; 0,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,28</t>
+          <t>-4,06; 0,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 5,45</t>
+          <t>-2,16; 5,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 4,65</t>
+          <t>-3,03; 4,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,97; -2,0</t>
+          <t>-7,06; -1,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,14</t>
+          <t>-2,25; 2,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,84</t>
+          <t>-2,51; 1,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,35; -1,51</t>
+          <t>-5,11; -1,39</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-61,25%</t>
+          <t>-66,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-69,64%</t>
+          <t>-58,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-65,46%</t>
+          <t>-60,42%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-85,88; 35,62</t>
+          <t>-85,38; 38,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-84,84; 24,61</t>
+          <t>-84,88; 26,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-91,9; 55,47</t>
+          <t>-92,5; 53,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 108,01</t>
+          <t>-28,59; 112,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 91,9</t>
+          <t>-36,33; 90,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-86,44; -36,71</t>
+          <t>-78,47; -22,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,21; 54,41</t>
+          <t>-36,8; 54,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 47,91</t>
+          <t>-40,47; 44,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,14; -32,93</t>
+          <t>-77,17; -27,75</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>2,71</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,36</t>
+          <t>2,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,55</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,86</t>
+          <t>-1,34; 0,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,79</t>
+          <t>0,66; 4,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 10,13</t>
+          <t>-1,02; 9,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 1,68</t>
+          <t>-5,9; 1,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 7,35</t>
+          <t>-2,21; 6,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 6,07</t>
+          <t>-0,26; 5,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,05</t>
+          <t>-3,64; 0,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,57</t>
+          <t>0,18; 4,78</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>606,19%</t>
+          <t>540,62%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>117,08%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 370,13</t>
+          <t>-20,54; 298,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-81,82; 69,58</t>
+          <t>-80,65; 85,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 252,16</t>
+          <t>-26,61; 229,57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,42; 350,26</t>
+          <t>-14,02; 313,66</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-77,0; 79,88</t>
+          <t>-79,88; 57,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,16; 355,56</t>
+          <t>-0,48; 286,07</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,52</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 0,5</t>
+          <t>-3,12; 0,75</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,19</t>
+          <t>-2,85; 1,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,96</t>
+          <t>-1,32; 3,02</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 2,24</t>
+          <t>-5,62; 2,44</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 0,93</t>
+          <t>-6,61; 0,8</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 3,79</t>
+          <t>-3,69; 3,56</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,69</t>
+          <t>-3,36; 0,97</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,26</t>
+          <t>-4,1; 0,2</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,73</t>
+          <t>-1,57; 2,78</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 224,06</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 299,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 398,19</t>
+          <t>-47,31; 402,56</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,9; 56,38</t>
+          <t>-63,43; 60,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-72,76; 31,9</t>
+          <t>-75,36; 19,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-37,62; 95,06</t>
+          <t>-41,46; 78,79</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-64,64; 26,19</t>
+          <t>-63,98; 32,01</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-73,48; 11,91</t>
+          <t>-72,66; 13,15</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-31,77; 89,13</t>
+          <t>-29,61; 90,3</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>2,44</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -0,01</t>
+          <t>-3,39; 0,08</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,2</t>
+          <t>-2,44; 1,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,32</t>
+          <t>-0,27; 4,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 2,81</t>
+          <t>-2,93; 2,52</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,3; -0,49</t>
+          <t>-5,4; -0,38</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 3,58</t>
+          <t>0,2; 5,83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,73</t>
+          <t>-2,57; 0,68</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,32; -0,07</t>
+          <t>-3,28; -0,06</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,93</t>
+          <t>0,7; 4,22</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-83,1; 13,62</t>
+          <t>-84,48; 11,24</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-59,26; 63,52</t>
+          <t>-59,68; 73,85</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 161,01</t>
+          <t>-10,68; 223,61</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 54,05</t>
+          <t>-37,44; 48,04</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-66,24; -8,64</t>
+          <t>-66,54; -7,98</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-55,48; 61,0</t>
+          <t>0,62; 114,98</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-45,31; 19,35</t>
+          <t>-44,21; 18,63</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-56,99; -0,51</t>
+          <t>-57,61; -0,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 71,64</t>
+          <t>11,27; 107,54</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,29</t>
+          <t>-2,24</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,99</t>
+          <t>-1,87</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -0,54</t>
+          <t>-3,21; -0,56</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,35</t>
+          <t>-3,03; -0,37</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,84; -1,27</t>
+          <t>-3,51; -1,18</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,06</t>
+          <t>-1,0; 2,89</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,04</t>
+          <t>-1,64; 1,87</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -0,04</t>
+          <t>-3,21; -0,16</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,84</t>
+          <t>-1,53; 0,79</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,54</t>
+          <t>-1,85; 0,47</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,11; -1,07</t>
+          <t>-2,96; -0,99</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-92,37%</t>
+          <t>-90,58%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-42,99%</t>
+          <t>-44,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-67,93%</t>
+          <t>-63,89%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-91,35; -19,75</t>
+          <t>-91,16; -22,07</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-85,74; -3,09</t>
+          <t>-85,34; -3,19</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -67,42</t>
+          <t>-100,0; -49,25</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 123,17</t>
+          <t>-25,23; 108,32</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-38,23; 81,25</t>
+          <t>-37,78; 73,66</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-68,06; 2,17</t>
+          <t>-69,71; -5,23</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 38,94</t>
+          <t>-43,63; 33,34</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 26,83</t>
+          <t>-50,43; 20,69</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-83,03; -45,79</t>
+          <t>-78,63; -42,01</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>0,01</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,58; -0,25</t>
+          <t>-1,58; -0,23</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,3</t>
+          <t>-1,68; -0,29</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,41</t>
+          <t>-0,8; 0,63</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,74</t>
+          <t>-0,49; 1,79</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,36; -0,14</t>
+          <t>-2,24; -0,18</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,61</t>
+          <t>-0,98; 0,99</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,67</t>
+          <t>-0,76; 0,57</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,65; -0,43</t>
+          <t>-1,66; -0,45</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,38</t>
+          <t>-0,64; 0,58</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-10,97%</t>
+          <t>-2,48%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-6,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-7,56%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-61,17; -12,84</t>
+          <t>-61,02; -10,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-60,5; -15,87</t>
+          <t>-63,34; -16,04</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 22,73</t>
+          <t>-30,88; 33,52</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 37,26</t>
+          <t>-8,75; 37,27</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-40,08; -3,02</t>
+          <t>-37,43; -2,8</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 13,14</t>
+          <t>-16,28; 20,5</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 19,7</t>
+          <t>-18,28; 16,09</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-39,86; -12,22</t>
+          <t>-39,26; -13,36</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 11,58</t>
+          <t>-15,26; 16,7</t>
         </is>
       </c>
     </row>
